--- a/artfynd/A 49374-2025 artfynd.xlsx
+++ b/artfynd/A 49374-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55170432</v>
+        <v>15098699</v>
       </c>
       <c r="B2" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,28 +705,34 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Palmsgården NO, Dlr</t>
+          <t>Dalagården, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549449.7470281341</v>
+        <v>549396</v>
       </c>
       <c r="R2" t="n">
-        <v>6732005.336226215</v>
+        <v>6731973</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,22 +759,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-07-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-06-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-07-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-06-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Har varit en fin skogsglänta, men ligger nu öppet i kanten på ett hygge.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,39 +780,39 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Hygge</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Urban Gunnarsson</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Urban Gunnarsson</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
+          <t>Falu kommun inventering ansvarsarter</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60553547</v>
+        <v>55170432</v>
       </c>
       <c r="B3" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -839,10 +835,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -853,13 +853,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549438.8799485188</v>
+        <v>549450</v>
       </c>
       <c r="R3" t="n">
-        <v>6731975.822419289</v>
+        <v>6732005</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,22 +883,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-06-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-06-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,19 +919,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89123768</v>
+        <v>55170448</v>
       </c>
       <c r="B4" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -964,27 +949,31 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Palmsgården, Dlr</t>
+          <t>Palmsgården NO, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549549.7708478516</v>
+        <v>549419</v>
       </c>
       <c r="R4" t="n">
-        <v>6731897.091463146</v>
+        <v>6732044</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,27 +997,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:50</t>
+          <t>2015-07-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>18:32</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Biogeografisk övervakning. Tot 7 ex på hela slingan Palmsgården. Lite moln, starttemp 23°C, sluttemp  23°C. sydvästlig vind (3), sol 100% av tiden.</t>
+          <t>2015-07-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,12 +1017,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marianne Pasanen-Mortensen</t>
+          <t>Urban Gunnarsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marianne Pasanen-Mortensen</t>
+          <t>Urban Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1059,19 +1033,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110135318</v>
+        <v>56111325</v>
       </c>
       <c r="B5" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1094,35 +1063,42 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>friflygande</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Palmsgården, Dlr</t>
+          <t>Hillersboda Palmsgården, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549507.76030179</v>
+        <v>549490</v>
       </c>
       <c r="R5" t="n">
-        <v>6731921.960130909</v>
+        <v>6731942</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,27 +1122,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2014-06-15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2014-06-15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Biogeografisk övervakning. Totalt 18 ex. på slingan Palmsgården. Inv.tid kl. 14.20 -16.05. Temp 25 grader. 100% sol (disigt). svag vind.</t>
+          <t>Biogeografisk uppföljning utförd av Länsstyrelsen i Dalarna på uppdrag av Naturvårdsverket via Lunds Universitet</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,19 +1151,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jonas Eriksson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jonas Eriksson</t>
+          <t>Urban Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1198,19 +1173,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110135581</v>
+        <v>56111326</v>
       </c>
       <c r="B6" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1233,35 +1203,42 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>friflygande</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Palmsgården, Dlr</t>
+          <t>Hillersboda Palmsgården, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549551.7245072247</v>
+        <v>549413</v>
       </c>
       <c r="R6" t="n">
-        <v>6731897.60788673</v>
+        <v>6732040</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1285,27 +1262,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2014-06-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2014-06-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Biogeografisk övervakning. Totalt 18 ex. på slingan Palmsgården. Inv.tid kl. 14.20 -16.05. Temp 25 grader. 100% sol (disigt). svag vind.</t>
+          <t>Biogeografisk uppföljning utförd av Länsstyrelsen i Dalarna på uppdrag av Naturvårdsverket via Lunds Universitet</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,22 +1291,895 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Urban Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>60553547</v>
+      </c>
+      <c r="B7" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Palmsgården NO, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>549439</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6731976</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2016-06-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2016-06-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Urban Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Urban Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>66408343</v>
+      </c>
+      <c r="B8" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hillerboda, PalmsgårdenDalagården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>549494</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6731934</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-06-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-06-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning, 13 st på slingan</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Blomkvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>89123768</v>
+      </c>
+      <c r="B9" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Palmsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>549550</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6731897</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-06-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-06-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Tot 7 ex på hela slingan Palmsgården. Lite moln, starttemp 23°C, sluttemp  23°C. sydvästlig vind (3), sol 100% av tiden.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marianne Pasanen-Mortensen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marianne Pasanen-Mortensen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>95271931</v>
+      </c>
+      <c r="B10" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Palmsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>549491</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6731934</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Soligt med slöjmoln. Vind 5 vid sjön, vindstilla i skogen. Temp. 20-23 grader. Tid kl. 10.17-13.22. Totalt 8 ex på slingan.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Jonas Eriksson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Jonas Eriksson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>101703425</v>
+      </c>
+      <c r="B11" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Palmsgården, Hillersboda, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>549578</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6731885</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-06-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-06-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Totalt 5 bg på sträckan. 16-21 grader. Vind 1. Sol 75 % av tiden.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jonas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jonas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>110135318</v>
+      </c>
+      <c r="B12" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Palmsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>549507</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6731922</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Totalt 18 ex. på slingan Palmsgården. Inv.tid kl. 14.20 -16.05. Temp 25 grader. 100% sol (disigt). svag vind.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jonas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jonas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>110135581</v>
+      </c>
+      <c r="B13" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Palmsgården, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>549552</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6731898</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Biogeografisk övervakning. Totalt 18 ex. på slingan Palmsgården. Inv.tid kl. 14.20 -16.05. Temp 25 grader. 100% sol (disigt). svag vind.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jonas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jonas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>

--- a/artfynd/A 49374-2025 artfynd.xlsx
+++ b/artfynd/A 49374-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -800,6 +805,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Falu kommun inventering ansvarsarter</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15098699</t>
         </is>
       </c>
     </row>
@@ -916,6 +926,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55170432</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,6 +1045,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55170448</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1170,6 +1190,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56111325</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1308,6 +1333,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56111326</t>
         </is>
       </c>
     </row>
@@ -1420,6 +1450,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60553547</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1540,6 +1575,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66408343</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1665,6 +1705,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123768</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1789,6 +1834,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95271931</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1916,6 +1966,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101703425</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2050,6 +2105,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110135318</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2184,8 +2244,27 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110135581</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>